--- a/RAW_DATA_XLSX/NPL_raw_data.xlsx
+++ b/RAW_DATA_XLSX/NPL_raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,52 +429,57 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>BX.KLT.DINV.WD.GD.ZS</t>
+          <t>education</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>FP.CPI.TOTL.ZG</t>
+          <t>fdi</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>NE.TRD.GNFS.ZS</t>
+          <t>gdp_growth</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>NV.IND.TOTL.ZS</t>
+          <t>gdp_pc</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>NY.GDP.MKTP.KD.ZG</t>
+          <t>log_gdp_pc</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>NY.GDP.PCAP.KD</t>
+          <t>gini</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>SE.SEC.ENRR</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>SI.POV.GINI</t>
+          <t>inflation</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>SL.UEM.TOTL.ZS</t>
+          <t>trade</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>SP.URB.TOTL.IN.ZS</t>
+          <t>unemployment</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>urban</t>
         </is>
       </c>
     </row>
@@ -487,32 +492,35 @@
       <c r="B2" t="n">
         <v>1995</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
+      <c r="C2" t="n">
+        <v>40.1949615478516</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>3.46845189309603</v>
+      </c>
+      <c r="F2" t="n">
+        <v>477.741099613336</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.169068953147444</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>21.2738679137675</v>
+      </c>
+      <c r="J2" t="n">
         <v>7.62296950698163</v>
       </c>
-      <c r="E2" t="n">
+      <c r="K2" t="n">
         <v>59.49051839854</v>
       </c>
-      <c r="F2" t="n">
-        <v>21.2738679137675</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.46845189309603</v>
-      </c>
-      <c r="H2" t="n">
-        <v>477.741099613336</v>
-      </c>
-      <c r="I2" t="n">
-        <v>40.1949615478516</v>
-      </c>
-      <c r="J2" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>10.473</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>24.1000758705435</v>
       </c>
     </row>
@@ -526,31 +534,34 @@
         <v>1996</v>
       </c>
       <c r="C3" t="n">
+        <v>43.1790885925293</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.423749430010865</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>5.32828417508708</v>
+      </c>
+      <c r="F3" t="n">
+        <v>492.212428031946</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.1989103876015</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>21.4930517891794</v>
+      </c>
+      <c r="J3" t="n">
         <v>9.220466623769861</v>
       </c>
-      <c r="E3" t="n">
+      <c r="K3" t="n">
         <v>58.4577686983002</v>
       </c>
-      <c r="F3" t="n">
-        <v>21.4930517891794</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.32828417508708</v>
-      </c>
-      <c r="H3" t="n">
-        <v>492.212428031946</v>
-      </c>
-      <c r="I3" t="n">
-        <v>43.1790885925293</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>10.446</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>25.2906817030471</v>
       </c>
     </row>
@@ -563,30 +574,33 @@
       <c r="B4" t="n">
         <v>1997</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
         <v>0.468752021000606</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>5.04861254517328</v>
+      </c>
+      <c r="F4" t="n">
+        <v>506.426874424217</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.227379938979918</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>21.4004342044754</v>
+      </c>
+      <c r="J4" t="n">
         <v>4.00998860523181</v>
       </c>
-      <c r="E4" t="n">
+      <c r="K4" t="n">
         <v>64.03553489499591</v>
       </c>
-      <c r="F4" t="n">
-        <v>21.4004342044754</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.04861254517328</v>
-      </c>
-      <c r="H4" t="n">
-        <v>506.426874424217</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>10.512</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>26.5867669012845</v>
       </c>
     </row>
@@ -599,30 +613,33 @@
       <c r="B5" t="n">
         <v>1998</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
         <v>0.247611787038703</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>3.01638947539399</v>
+      </c>
+      <c r="F5" t="n">
+        <v>511.54871132025</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.237442813155027</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>21.0759693529891</v>
+      </c>
+      <c r="J5" t="n">
         <v>11.2444677818614</v>
       </c>
-      <c r="E5" t="n">
+      <c r="K5" t="n">
         <v>56.7096012897007</v>
       </c>
-      <c r="F5" t="n">
-        <v>21.0759693529891</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.01638947539399</v>
-      </c>
-      <c r="H5" t="n">
-        <v>511.54871132025</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>10.526</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>27.9874840142543</v>
       </c>
     </row>
@@ -636,31 +653,34 @@
         <v>1999</v>
       </c>
       <c r="C6" t="n">
+        <v>33.1490211486816</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.08643976568271559</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>4.41257328041399</v>
+      </c>
+      <c r="F6" t="n">
+        <v>524.27256909301</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.26201171910434</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>20.4411231566268</v>
+      </c>
+      <c r="J6" t="n">
         <v>7.45111260957546</v>
       </c>
-      <c r="E6" t="n">
+      <c r="K6" t="n">
         <v>52.5669812534353</v>
       </c>
-      <c r="F6" t="n">
-        <v>20.4411231566268</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.41257328041399</v>
-      </c>
-      <c r="H6" t="n">
-        <v>524.27256909301</v>
-      </c>
-      <c r="I6" t="n">
-        <v>33.1490211486816</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>10.549</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>29.4919855909549</v>
       </c>
     </row>
@@ -674,31 +694,34 @@
         <v>2000</v>
       </c>
       <c r="C7" t="n">
+        <v>34.4201507568359</v>
+      </c>
+      <c r="D7" t="n">
         <v>-0.00882425294523833</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>6.19999998192236</v>
+      </c>
+      <c r="F7" t="n">
+        <v>547.221082273632</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.304852893113016</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>20.7355700311999</v>
+      </c>
+      <c r="J7" t="n">
         <v>2.47882020709136</v>
       </c>
-      <c r="E7" t="n">
+      <c r="K7" t="n">
         <v>55.7105890041319</v>
       </c>
-      <c r="F7" t="n">
-        <v>20.7355700311999</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.19999998192236</v>
-      </c>
-      <c r="H7" t="n">
-        <v>547.221082273632</v>
-      </c>
-      <c r="I7" t="n">
-        <v>34.4201507568359</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>10.531</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>31.0994241803849</v>
       </c>
     </row>
@@ -712,31 +735,34 @@
         <v>2001</v>
       </c>
       <c r="C8" t="n">
+        <v>37.3896903991699</v>
+      </c>
+      <c r="D8" t="n">
         <v>0.347091875363344</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>4.79989214255407</v>
+      </c>
+      <c r="F8" t="n">
+        <v>564.28622920391</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.335561621352696</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>16.6609082977555</v>
+      </c>
+      <c r="J8" t="n">
         <v>2.6883037354563</v>
       </c>
-      <c r="E8" t="n">
+      <c r="K8" t="n">
         <v>55.7999210803706</v>
       </c>
-      <c r="F8" t="n">
-        <v>16.6609082977555</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4.79989214255407</v>
-      </c>
-      <c r="H8" t="n">
-        <v>564.28622920391</v>
-      </c>
-      <c r="I8" t="n">
-        <v>37.3896903991699</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>10.502</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>32.808952331543</v>
       </c>
     </row>
@@ -750,31 +776,34 @@
         <v>2002</v>
       </c>
       <c r="C9" t="n">
+        <v>41.0556297302246</v>
+      </c>
+      <c r="D9" t="n">
         <v>-0.0983748686510898</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>0.120143177369414</v>
+      </c>
+      <c r="F9" t="n">
+        <v>556.438454538796</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.32155657077898</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>16.9468247421334</v>
+      </c>
+      <c r="J9" t="n">
         <v>3.02939948714892</v>
       </c>
-      <c r="E9" t="n">
+      <c r="K9" t="n">
         <v>46.2307185004451</v>
       </c>
-      <c r="F9" t="n">
-        <v>16.9468247421334</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.120143177369414</v>
-      </c>
-      <c r="H9" t="n">
-        <v>556.438454538796</v>
-      </c>
-      <c r="I9" t="n">
-        <v>41.0556297302246</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>10.593</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>35.0358944291182</v>
       </c>
     </row>
@@ -788,33 +817,36 @@
         <v>2003</v>
       </c>
       <c r="C10" t="n">
+        <v>42.0749092102051</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.233443620739643</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>3.94503776051116</v>
+      </c>
+      <c r="F10" t="n">
+        <v>570.28967363428</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.346144431097422</v>
+      </c>
+      <c r="H10" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>16.9713000603375</v>
+      </c>
+      <c r="J10" t="n">
         <v>5.70700931874738</v>
       </c>
-      <c r="E10" t="n">
+      <c r="K10" t="n">
         <v>44.2478836156195</v>
       </c>
-      <c r="F10" t="n">
-        <v>16.9713000603375</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.94503776051116</v>
-      </c>
-      <c r="H10" t="n">
-        <v>570.28967363428</v>
-      </c>
-      <c r="I10" t="n">
-        <v>42.0749092102051</v>
-      </c>
-      <c r="J10" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>10.644</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>38.045308394296</v>
       </c>
     </row>
@@ -827,30 +859,33 @@
       <c r="B11" t="n">
         <v>2004</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
         <v>-0.00573755737053384</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>4.68260325152944</v>
+      </c>
+      <c r="F11" t="n">
+        <v>589.46992868617</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.379223707117632</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>16.6573202744672</v>
+      </c>
+      <c r="J11" t="n">
         <v>2.8418113124898</v>
       </c>
-      <c r="E11" t="n">
+      <c r="K11" t="n">
         <v>46.1472867206087</v>
       </c>
-      <c r="F11" t="n">
-        <v>16.6573202744672</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.68260325152944</v>
-      </c>
-      <c r="H11" t="n">
-        <v>589.46992868617</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>10.652</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>41.6109470808194</v>
       </c>
     </row>
@@ -864,31 +899,34 @@
         <v>2005</v>
       </c>
       <c r="C12" t="n">
+        <v>45.098201751709</v>
+      </c>
+      <c r="D12" t="n">
         <v>0.030156295078659</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>3.47918104829496</v>
+      </c>
+      <c r="F12" t="n">
+        <v>603.190108570995</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.402232418301659</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>16.4670892346949</v>
+      </c>
+      <c r="J12" t="n">
         <v>6.83633265892877</v>
       </c>
-      <c r="E12" t="n">
+      <c r="K12" t="n">
         <v>44.0629474798613</v>
       </c>
-      <c r="F12" t="n">
-        <v>16.4670892346949</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3.47918104829496</v>
-      </c>
-      <c r="H12" t="n">
-        <v>603.190108570995</v>
-      </c>
-      <c r="I12" t="n">
-        <v>45.098201751709</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10.59</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>45.5065633424317</v>
       </c>
     </row>
@@ -902,31 +940,34 @@
         <v>2006</v>
       </c>
       <c r="C13" t="n">
+        <v>42.5181617736816</v>
+      </c>
+      <c r="D13" t="n">
         <v>-0.07350943325941101</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>3.36461478056277</v>
+      </c>
+      <c r="F13" t="n">
+        <v>617.477638588722</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.425642855034646</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>16.0679668054868</v>
+      </c>
+      <c r="J13" t="n">
         <v>6.92033580707589</v>
       </c>
-      <c r="E13" t="n">
+      <c r="K13" t="n">
         <v>44.7619877569242</v>
       </c>
-      <c r="F13" t="n">
-        <v>16.0679668054868</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.36461478056277</v>
-      </c>
-      <c r="H13" t="n">
-        <v>617.477638588722</v>
-      </c>
-      <c r="I13" t="n">
-        <v>42.5181617736816</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>10.609</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>49.5059100328759</v>
       </c>
     </row>
@@ -940,31 +981,34 @@
         <v>2007</v>
       </c>
       <c r="C14" t="n">
+        <v>42.0970306396484</v>
+      </c>
+      <c r="D14" t="n">
         <v>0.0556064154566332</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>3.41156027980276</v>
+      </c>
+      <c r="F14" t="n">
+        <v>633.226129136597</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.450827592374355</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>15.873140183038</v>
+      </c>
+      <c r="J14" t="n">
         <v>2.26921924439074</v>
       </c>
-      <c r="E14" t="n">
+      <c r="K14" t="n">
         <v>44.5792750200254</v>
       </c>
-      <c r="F14" t="n">
-        <v>15.873140183038</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3.41156027980276</v>
-      </c>
-      <c r="H14" t="n">
-        <v>633.226129136597</v>
-      </c>
-      <c r="I14" t="n">
-        <v>42.0970306396484</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>10.642</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>53.3827400058951</v>
       </c>
     </row>
@@ -978,31 +1022,34 @@
         <v>2008</v>
       </c>
       <c r="C15" t="n">
+        <v>48.0189094543457</v>
+      </c>
+      <c r="D15" t="n">
         <v>0.00793215735192788</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>6.10463914373472</v>
+      </c>
+      <c r="F15" t="n">
+        <v>666.865095417138</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6.502587769712752</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>16.049986636556</v>
+      </c>
+      <c r="J15" t="n">
         <v>9.907830053064799</v>
       </c>
-      <c r="E15" t="n">
+      <c r="K15" t="n">
         <v>46.0362063511913</v>
       </c>
-      <c r="F15" t="n">
-        <v>16.049986636556</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6.10463914373472</v>
-      </c>
-      <c r="H15" t="n">
-        <v>666.865095417138</v>
-      </c>
-      <c r="I15" t="n">
-        <v>48.0189094543457</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>10.597</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>56.9108061152324</v>
       </c>
     </row>
@@ -1016,31 +1063,34 @@
         <v>2009</v>
       </c>
       <c r="C16" t="n">
+        <v>49.2625999450684</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.297715388957693</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>4.5330787246486</v>
+      </c>
+      <c r="F16" t="n">
+        <v>692.400000816919</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.540163824481891</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>15.0668034711092</v>
+      </c>
+      <c r="J16" t="n">
         <v>11.0948237386987</v>
       </c>
-      <c r="E16" t="n">
+      <c r="K16" t="n">
         <v>47.0794477633688</v>
       </c>
-      <c r="F16" t="n">
-        <v>15.0668034711092</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4.5330787246486</v>
-      </c>
-      <c r="H16" t="n">
-        <v>692.400000816919</v>
-      </c>
-      <c r="I16" t="n">
-        <v>49.2625999450684</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>10.582</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>59.8638612146309</v>
       </c>
     </row>
@@ -1054,33 +1104,36 @@
         <v>2010</v>
       </c>
       <c r="C17" t="n">
+        <v>55.5892906188965</v>
+      </c>
+      <c r="D17" t="n">
         <v>0.548294665887946</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>4.81641464694573</v>
+      </c>
+      <c r="F17" t="n">
+        <v>721.265221364302</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.581006921744232</v>
+      </c>
+      <c r="H17" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>14.2007622567226</v>
+      </c>
+      <c r="J17" t="n">
         <v>9.32650410745395</v>
       </c>
-      <c r="E17" t="n">
+      <c r="K17" t="n">
         <v>45.9849057742707</v>
       </c>
-      <c r="F17" t="n">
-        <v>14.2007622567226</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.81641464694573</v>
-      </c>
-      <c r="H17" t="n">
-        <v>721.265221364302</v>
-      </c>
-      <c r="I17" t="n">
-        <v>55.5892906188965</v>
-      </c>
-      <c r="J17" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>10.563</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>62.0156581578338</v>
       </c>
     </row>
@@ -1094,31 +1147,34 @@
         <v>2011</v>
       </c>
       <c r="C18" t="n">
+        <v>58.9935111999512</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.435814930594323</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>3.42180870116162</v>
+      </c>
+      <c r="F18" t="n">
+        <v>742.617252662576</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.610180774253302</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>13.393470598846</v>
+      </c>
+      <c r="J18" t="n">
         <v>9.2270754612596</v>
       </c>
-      <c r="E18" t="n">
+      <c r="K18" t="n">
         <v>36.296758890097</v>
       </c>
-      <c r="F18" t="n">
-        <v>13.393470598846</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.42180870116162</v>
-      </c>
-      <c r="H18" t="n">
-        <v>742.617252662576</v>
-      </c>
-      <c r="I18" t="n">
-        <v>58.9935111999512</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>10.627</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>63.139949798584</v>
       </c>
     </row>
@@ -1132,31 +1188,34 @@
         <v>2012</v>
       </c>
       <c r="C19" t="n">
+        <v>63.1414794921875</v>
+      </c>
+      <c r="D19" t="n">
         <v>0.42369151125933</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>4.67014192446953</v>
+      </c>
+      <c r="F19" t="n">
+        <v>775.310578479839</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.653263695501543</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>13.9771618084251</v>
+      </c>
+      <c r="J19" t="n">
         <v>9.45980980357125</v>
       </c>
-      <c r="E19" t="n">
+      <c r="K19" t="n">
         <v>37.921906058758</v>
       </c>
-      <c r="F19" t="n">
-        <v>13.9771618084251</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4.67014192446953</v>
-      </c>
-      <c r="H19" t="n">
-        <v>775.310578479839</v>
-      </c>
-      <c r="I19" t="n">
-        <v>63.1414794921875</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>10.632</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>63.6558406194333</v>
       </c>
     </row>
@@ -1170,31 +1229,34 @@
         <v>2013</v>
       </c>
       <c r="C20" t="n">
+        <v>65.4935302734375</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.334712330597339</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>3.52515317129149</v>
+      </c>
+      <c r="F20" t="n">
+        <v>801.039060847856</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6.685909710982821</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>13.7983375627601</v>
+      </c>
+      <c r="J20" t="n">
         <v>9.04016311917645</v>
       </c>
-      <c r="E20" t="n">
+      <c r="K20" t="n">
         <v>41.8653757376722</v>
       </c>
-      <c r="F20" t="n">
-        <v>13.7983375627601</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.52515317129149</v>
-      </c>
-      <c r="H20" t="n">
-        <v>801.039060847856</v>
-      </c>
-      <c r="I20" t="n">
-        <v>65.4935302734375</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>10.666</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>64.13145701560479</v>
       </c>
     </row>
@@ -1208,31 +1270,34 @@
         <v>2014</v>
       </c>
       <c r="C21" t="n">
+        <v>67.5318298339844</v>
+      </c>
+      <c r="D21" t="n">
         <v>0.133746236524448</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>6.01148284250441</v>
+      </c>
+      <c r="F21" t="n">
+        <v>846.665541773599</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.741305742729731</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>13.5645652301586</v>
+      </c>
+      <c r="J21" t="n">
         <v>8.36415469659563</v>
       </c>
-      <c r="E21" t="n">
+      <c r="K21" t="n">
         <v>45.9826416115927</v>
       </c>
-      <c r="F21" t="n">
-        <v>13.5645652301586</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.01148284250441</v>
-      </c>
-      <c r="H21" t="n">
-        <v>846.665541773599</v>
-      </c>
-      <c r="I21" t="n">
-        <v>67.5318298339844</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>10.62</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>64.5640847098488</v>
       </c>
     </row>
@@ -1246,31 +1311,34 @@
         <v>2015</v>
       </c>
       <c r="C22" t="n">
+        <v>68.6131210327148</v>
+      </c>
+      <c r="D22" t="n">
         <v>0.213029527712984</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>3.97605327162971</v>
+      </c>
+      <c r="F22" t="n">
+        <v>875.543635474862</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.77484499111767</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>13.1616546296789</v>
+      </c>
+      <c r="J22" t="n">
         <v>7.86890895590891</v>
       </c>
-      <c r="E22" t="n">
+      <c r="K22" t="n">
         <v>46.6657303895158</v>
       </c>
-      <c r="F22" t="n">
-        <v>13.1616546296789</v>
-      </c>
-      <c r="G22" t="n">
-        <v>3.97605327162971</v>
-      </c>
-      <c r="H22" t="n">
-        <v>875.543635474862</v>
-      </c>
-      <c r="I22" t="n">
-        <v>68.6131210327148</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>10.643</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>64.9510094249155</v>
       </c>
     </row>
@@ -1284,31 +1352,34 @@
         <v>2016</v>
       </c>
       <c r="C23" t="n">
+        <v>71.7744979858398</v>
+      </c>
+      <c r="D23" t="n">
         <v>0.432212944008614</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>0.433113719381524</v>
+      </c>
+      <c r="F23" t="n">
+        <v>875.188943730855</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.774439798739264</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>12.6554177701811</v>
+      </c>
+      <c r="J23" t="n">
         <v>8.7903433200464</v>
       </c>
-      <c r="E23" t="n">
+      <c r="K23" t="n">
         <v>42.115486124737</v>
       </c>
-      <c r="F23" t="n">
-        <v>12.6554177701811</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.433113719381524</v>
-      </c>
-      <c r="H23" t="n">
-        <v>875.188943730855</v>
-      </c>
-      <c r="I23" t="n">
-        <v>71.7744979858398</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>10.714</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>65.28951688355529</v>
       </c>
     </row>
@@ -1322,31 +1393,34 @@
         <v>2017</v>
       </c>
       <c r="C24" t="n">
+        <v>74.4113311767578</v>
+      </c>
+      <c r="D24" t="n">
         <v>0.6774398841829909</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>8.977279356434661</v>
+      </c>
+      <c r="F24" t="n">
+        <v>951.8572985636411</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6.858415127089003</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>12.8625858899927</v>
+      </c>
+      <c r="J24" t="n">
         <v>2.77703998300211</v>
       </c>
-      <c r="E24" t="n">
+      <c r="K24" t="n">
         <v>44.6424106224996</v>
       </c>
-      <c r="F24" t="n">
-        <v>12.8625858899927</v>
-      </c>
-      <c r="G24" t="n">
-        <v>8.977279356434661</v>
-      </c>
-      <c r="H24" t="n">
-        <v>951.8572985636411</v>
-      </c>
-      <c r="I24" t="n">
-        <v>74.4113311767578</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>10.66</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>65.57689280851839</v>
       </c>
     </row>
@@ -1359,30 +1433,33 @@
       <c r="B25" t="n">
         <v>2018</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
         <v>0.206157201926214</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>7.62237610397935</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1021.91492204011</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.929433520762369</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>13.2006396343014</v>
+      </c>
+      <c r="J25" t="n">
         <v>4.40659410175714</v>
       </c>
-      <c r="E25" t="n">
+      <c r="K25" t="n">
         <v>48.4473869461067</v>
       </c>
-      <c r="F25" t="n">
-        <v>13.2006396343014</v>
-      </c>
-      <c r="G25" t="n">
-        <v>7.62237610397935</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1021.91492204011</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>10.593</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>65.81042292255511</v>
       </c>
     </row>
@@ -1396,31 +1473,34 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
+        <v>80.28005218505859</v>
+      </c>
+      <c r="D26" t="n">
         <v>0.542801979747667</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>6.65705543110467</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1077.11796498188</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6.982044202246393</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>13.0106754142894</v>
+      </c>
+      <c r="J26" t="n">
         <v>5.56616035243723</v>
       </c>
-      <c r="E26" t="n">
+      <c r="K26" t="n">
         <v>49.2495265874454</v>
       </c>
-      <c r="F26" t="n">
-        <v>13.0106754142894</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6.65705543110467</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1077.11796498188</v>
-      </c>
-      <c r="I26" t="n">
-        <v>80.28005218505859</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>10.477</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>65.9873929484157</v>
       </c>
     </row>
@@ -1434,31 +1514,34 @@
         <v>2020</v>
       </c>
       <c r="C27" t="n">
+        <v>85.31015777587891</v>
+      </c>
+      <c r="D27" t="n">
         <v>0.378739091402959</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>-2.3696206292072</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1031.53618783934</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6.938804414629165</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>12.047319925355</v>
+      </c>
+      <c r="J27" t="n">
         <v>5.05635826238499</v>
       </c>
-      <c r="E27" t="n">
+      <c r="K27" t="n">
         <v>40.9188741243442</v>
       </c>
-      <c r="F27" t="n">
-        <v>12.047319925355</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-2.3696206292072</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1031.53618783934</v>
-      </c>
-      <c r="I27" t="n">
-        <v>85.31015777587891</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>13.037</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>66.10508860885049</v>
       </c>
     </row>
@@ -1472,31 +1555,34 @@
         <v>2021</v>
       </c>
       <c r="C28" t="n">
+        <v>83.9220209713597</v>
+      </c>
+      <c r="D28" t="n">
         <v>0.531690906776232</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>4.838149614115</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1062.7888430629</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6.968651716147926</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>11.7920425516798</v>
+      </c>
+      <c r="J28" t="n">
         <v>4.12676744440695</v>
       </c>
-      <c r="E28" t="n">
+      <c r="K28" t="n">
         <v>43.0538047919129</v>
       </c>
-      <c r="F28" t="n">
-        <v>11.7920425516798</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4.838149614115</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1062.7888430629</v>
-      </c>
-      <c r="I28" t="n">
-        <v>83.9220209713597</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>12.241</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>66.144235274522</v>
       </c>
     </row>
@@ -1510,33 +1596,36 @@
         <v>2022</v>
       </c>
       <c r="C29" t="n">
+        <v>84.1026475876285</v>
+      </c>
+      <c r="D29" t="n">
         <v>0.160405404733603</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>5.6313145568451</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1113.55462341223</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.0153125410957</v>
+      </c>
+      <c r="H29" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" t="n">
+        <v>12.1812284731342</v>
+      </c>
+      <c r="J29" t="n">
         <v>7.6702057938028</v>
       </c>
-      <c r="E29" t="n">
+      <c r="K29" t="n">
         <v>48.9734014799428</v>
       </c>
-      <c r="F29" t="n">
-        <v>12.1812284731342</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5.6313145568451</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1113.55462341223</v>
-      </c>
-      <c r="I29" t="n">
-        <v>84.1026475876285</v>
-      </c>
-      <c r="J29" t="n">
-        <v>30</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>10.661</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>66.2992968721053</v>
       </c>
     </row>
@@ -1550,31 +1639,34 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
+        <v>89.8898815141438</v>
+      </c>
+      <c r="D30" t="n">
         <v>0.182279066044198</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>1.98254843628392</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1136.42769313825</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7.035645018864956</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>11.9717042539851</v>
+      </c>
+      <c r="J30" t="n">
         <v>7.11587261530826</v>
       </c>
-      <c r="E30" t="n">
+      <c r="K30" t="n">
         <v>41.5701502933145</v>
       </c>
-      <c r="F30" t="n">
-        <v>11.9717042539851</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.98254843628392</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1136.42769313825</v>
-      </c>
-      <c r="I30" t="n">
-        <v>89.8898815141438</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>10.437</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>66.5432933453944</v>
       </c>
     </row>
@@ -1588,31 +1680,34 @@
         <v>2024</v>
       </c>
       <c r="C31" t="n">
+        <v>90.38784621559159</v>
+      </c>
+      <c r="D31" t="n">
         <v>0.132590416512966</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>3.66537430744967</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1179.81272768386</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7.073110999512022</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>11.4245020172191</v>
+      </c>
+      <c r="J31" t="n">
         <v>4.6850965426577</v>
       </c>
-      <c r="E31" t="n">
+      <c r="K31" t="n">
         <v>40.5298226771909</v>
       </c>
-      <c r="F31" t="n">
-        <v>11.4245020172191</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3.66537430744967</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1179.81272768386</v>
-      </c>
-      <c r="I31" t="n">
-        <v>90.38784621559159</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>10.5</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>66.77234316302901</v>
       </c>
     </row>
@@ -1633,10 +1728,11 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
         <v>10.465</v>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
